--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T11:02:10+00:00</t>
+    <t>2024-11-28T08:25:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-28T08:25:00+00:00</t>
+    <t>2024-11-28T17:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-28T17:50:24+00:00</t>
+    <t>2024-11-30T09:54:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T09:54:10+00:00</t>
+    <t>2024-12-03T09:13:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-03T09:13:19+00:00</t>
+    <t>2024-12-03T10:04:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-03T10:04:50+00:00</t>
+    <t>2024-12-05T14:20:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-05T14:20:46+00:00</t>
+    <t>2024-12-10T07:51:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-10T07:51:08+00:00</t>
+    <t>2024-12-10T08:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.9.0</t>
+    <t>1.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-10T08:19:29+00:00</t>
+    <t>2024-12-10T08:34:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-10T08:34:20+00:00</t>
+    <t>2024-12-10T08:45:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-10T08:45:26+00:00</t>
+    <t>2024-12-18T07:23:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.nl/fhir/zorgviewer/StructureDefinition/Immunization</t>
+    <t>http://fhir.hl7.nl/zorgviewer/StructureDefinition/Immunization</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-18T07:23:17+00:00</t>
+    <t>2024-12-23T09:34:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-23T09:34:32+00:00</t>
+    <t>2024-12-23T15:35:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-23T15:35:28+00:00</t>
+    <t>2024-12-27T09:44:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-27T09:44:10+00:00</t>
+    <t>2024-12-27T09:59:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.10.0</t>
+    <t>1.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-27T09:59:08+00:00</t>
+    <t>2025-01-02T11:11:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-02T11:11:09+00:00</t>
+    <t>2025-01-02T12:37:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-02T12:37:15+00:00</t>
+    <t>2025-01-05T10:27:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-05T10:27:23+00:00</t>
+    <t>2025-01-05T10:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-05T10:53:29+00:00</t>
+    <t>2025-01-06T15:42:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T15:42:07+00:00</t>
+    <t>2025-01-06T15:50:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T15:50:28+00:00</t>
+    <t>2025-01-06T16:52:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T16:52:49+00:00</t>
+    <t>2025-01-06T17:00:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T17:00:55+00:00</t>
+    <t>2025-01-20T15:02:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-20T15:02:53+00:00</t>
+    <t>2025-01-28T20:06:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.11.0</t>
+    <t>1.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T20:06:40+00:00</t>
+    <t>2025-01-28T20:08:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T20:08:20+00:00</t>
+    <t>2025-01-28T20:50:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T20:50:34+00:00</t>
+    <t>2025-01-31T07:22:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T07:22:48+00:00</t>
+    <t>2025-01-31T13:40:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T13:40:12+00:00</t>
+    <t>2025-02-03T11:19:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T11:19:03+00:00</t>
+    <t>2025-02-03T16:53:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T16:53:34+00:00</t>
+    <t>2025-02-04T12:12:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T12:12:36+00:00</t>
+    <t>2025-02-05T13:44:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T13:44:35+00:00</t>
+    <t>2025-02-05T14:01:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T14:01:06+00:00</t>
+    <t>2025-02-05T14:12:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T14:12:35+00:00</t>
+    <t>2025-02-12T15:28:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T15:28:44+00:00</t>
+    <t>2025-02-13T13:25:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T13:25:12+00:00</t>
+    <t>2025-02-13T13:30:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T13:30:29+00:00</t>
+    <t>2025-02-18T14:04:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T14:04:23+00:00</t>
+    <t>2025-02-24T11:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T11:20:06+00:00</t>
+    <t>2025-02-24T11:23:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T11:23:09+00:00</t>
+    <t>2025-02-24T11:25:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T11:25:44+00:00</t>
+    <t>2025-02-24T11:27:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T11:27:07+00:00</t>
+    <t>2025-02-24T13:31:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:31:19+00:00</t>
+    <t>2025-02-24T15:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T15:55:23+00:00</t>
+    <t>2025-02-24T16:22:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T16:22:43+00:00</t>
+    <t>2025-02-25T09:38:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T09:38:10+00:00</t>
+    <t>2025-02-25T09:39:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T09:39:04+00:00</t>
+    <t>2025-02-25T20:48:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:48:56+00:00</t>
+    <t>2025-02-25T21:05:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T21:05:22+00:00</t>
+    <t>2025-02-26T07:46:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-26T07:46:44+00:00</t>
+    <t>2025-02-26T13:03:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-26T13:03:44+00:00</t>
+    <t>2025-02-26T13:09:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-26T13:09:25+00:00</t>
+    <t>2025-02-26T14:34:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-26T14:34:33+00:00</t>
+    <t>2025-02-26T14:37:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-26T14:37:20+00:00</t>
+    <t>2025-02-28T09:54:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T09:54:46+00:00</t>
+    <t>2025-02-28T10:33:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T10:33:33+00:00</t>
+    <t>2025-02-28T10:57:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T10:57:51+00:00</t>
+    <t>2025-02-28T11:01:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T11:01:07+00:00</t>
+    <t>2025-02-28T11:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T11:11:13+00:00</t>
+    <t>2025-02-28T11:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T11:13:38+00:00</t>
+    <t>2025-02-28T11:38:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T11:38:05+00:00</t>
+    <t>2025-02-28T11:39:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T11:39:24+00:00</t>
+    <t>2025-02-28T11:59:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T11:59:16+00:00</t>
+    <t>2025-03-03T08:47:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-03T08:47:24+00:00</t>
+    <t>2025-03-04T09:51:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T09:51:39+00:00</t>
+    <t>2025-03-04T10:31:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T10:31:42+00:00</t>
+    <t>2025-03-05T06:48:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-05T06:48:27+00:00</t>
+    <t>2025-03-05T13:19:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-05T13:19:54+00:00</t>
+    <t>2025-03-05T13:45:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-05T13:45:25+00:00</t>
+    <t>2025-03-05T16:01:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-05T16:01:47+00:00</t>
+    <t>2025-03-06T16:40:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T16:40:55+00:00</t>
+    <t>2025-03-09T10:18:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-09T10:18:56+00:00</t>
+    <t>2025-03-09T10:31:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-09T10:31:47+00:00</t>
+    <t>2025-03-10T07:49:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-10T07:49:31+00:00</t>
+    <t>2025-03-10T07:56:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-10T07:56:47+00:00</t>
+    <t>2025-03-12T11:31:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T11:31:39+00:00</t>
+    <t>2025-03-12T11:55:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T11:55:43+00:00</t>
+    <t>2025-03-12T11:57:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T11:57:23+00:00</t>
+    <t>2025-03-13T10:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-13T10:18:09+00:00</t>
+    <t>2025-03-18T08:10:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T08:10:21+00:00</t>
+    <t>2025-03-18T10:21:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.12.0</t>
+    <t>1.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T10:21:48+00:00</t>
+    <t>2025-03-18T10:31:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T10:31:44+00:00</t>
+    <t>2025-03-18T13:21:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T13:21:59+00:00</t>
+    <t>2025-03-18T14:10:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T14:10:18+00:00</t>
+    <t>2025-03-24T10:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T10:28:29+00:00</t>
+    <t>2025-03-24T10:49:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T10:49:00+00:00</t>
+    <t>2025-03-24T11:21:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T11:21:14+00:00</t>
+    <t>2025-03-24T11:37:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T11:37:37+00:00</t>
+    <t>2025-04-01T10:33:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-01T10:33:26+00:00</t>
+    <t>2025-04-01T10:36:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.13.0</t>
+    <t>1.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-01T10:36:45+00:00</t>
+    <t>2025-04-01T10:40:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-01T10:40:06+00:00</t>
+    <t>2025-04-01T11:02:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-01T11:02:34+00:00</t>
+    <t>2025-04-07T09:57:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-07T09:57:36+00:00</t>
+    <t>2025-04-07T10:44:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-07T10:44:48+00:00</t>
+    <t>2025-04-07T14:17:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-07T14:17:30+00:00</t>
+    <t>2025-04-09T20:29:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-09T20:29:26+00:00</t>
+    <t>2025-04-09T20:35:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-09T20:35:07+00:00</t>
+    <t>2025-04-09T22:25:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Immunization.xlsx
+++ b/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-09T22:25:52+00:00</t>
+    <t>2025-04-09T23:03:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
